--- a/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\ПОКОМ КИ\pokom_ki\WholesaleCustomers\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF82BB1-6D9C-49FA-8D48-7C7D0E64DD78}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77EFF568-2D41-4680-935E-0795B87F7BF1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$G$2364</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$G$2407</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9776" uniqueCount="3224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9991" uniqueCount="3271">
   <si>
     <t>SU002447</t>
   </si>
@@ -9706,6 +9706,147 @@
   </si>
   <si>
     <t>Коныгин</t>
+  </si>
+  <si>
+    <t>Колбаса варено-копченая Мясорубская ТМ Стародворье с рубленой грудинкой фиброуз в/у ф/в 0,35 кг срез СК2</t>
+  </si>
+  <si>
+    <t>Колбаса варено-копченая Рубленая Запеченная ТМ Стародворье ТС Дугушка вектор ф/в 0,6 кг УВС1 СК1</t>
+  </si>
+  <si>
+    <t>Колбаса варено-копченая Салями Запеченная ТМ Стародворье ТС Дугушка вектор ф/в 0,6 кг УВС1 СК2</t>
+  </si>
+  <si>
+    <t>Колбаса варено-копченая Салями Мясорубская ТМ Стародворье с рубленым шпиком фиброуз в/у ф/в 0,35 кг срез СК2</t>
+  </si>
+  <si>
+    <t>Колбаса варено-копченая Салями Филейбургская зернистая ТМ Баварушка фиброуз в/у ф/в 0,35 кг срез УВС2 СК2</t>
+  </si>
+  <si>
+    <t>Колбаса варено-копченая Сервелат Запеченный ТМ Стародворье ТС Дугушка вектор ф/в 0,6 кг УВС1 СК2</t>
+  </si>
+  <si>
+    <t>Колбаса варено-копченая Сервелат Мясорубский ТМ Стародворье с мелкорубленным окороком фиброуз в/у вес СК2</t>
+  </si>
+  <si>
+    <t>Колбаса варено-копченая Сервелат Мясорубский ТМ Стародворье с мелкорубленным окороком фиброуз в/у ф/в 0,35 кг срез СК2</t>
+  </si>
+  <si>
+    <t>Колбаса варено-копченая Сервелат Филедворский ТМ Стародворье фиброуз в/у ф/в 0,35 кг срез НД2 СК2</t>
+  </si>
+  <si>
+    <t>Колбаса варено-копченая Сочинка по-европейски с сочной грудинкой ТМ Стародворье фиброуз в/у ф/в 0,3 кг срез СК2</t>
+  </si>
+  <si>
+    <t>Колбаса варено-копченая Сочинка по-фински с сочным окороком ТМ Стародворье фиброуз в/у ф/в 0,3 кг срез СК2</t>
+  </si>
+  <si>
+    <t>Колбаса полукопченая Кракушка пряная с сальцем ТМ Стародворье ТС Баварушка черева в/у ф/в 0,3 кг СК2</t>
+  </si>
+  <si>
+    <t>Колбаса полукопченая Сочинка зернистая с сочной грудинкой ТМ Стародворье фиброуз в/у вес СК2</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Докторская ТМ Стародворье ТС Дугушка полиамид ф/в 0,6 кг УВК СК3</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Докторский гарант ТМ Вязанка вектор ф/в 0,4 кг СК3</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Молокуша ТМ Вязанка полиамид ф/в 0,45 кг СК3</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Молочная по-стародворски ТМ Стародворье полиамид вес СК2</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Молочная Традиционная ТМ Стародворье полиамид вес СК1</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Сливушка ТМ Вязанка полиамид вес СК3</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Сливушка ТМ Вязанка полиамид 0,375 кг СК3</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Сливушка ТМ Вязанка полиамид 0,45 кг СК3</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Стародворская Традиционная со шпиком ТМ Стародворье полиамид вес СК1</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Филедворская по-стародворски ТМ Стародворье полиамид вес СК2</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Филейная ТМ Особый рецепт полиамид ф/в 0,5 кг СК4</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Филейская ТМ Вязанка ТС Классическая полиамид ф/в 0,45 кг НД СК3</t>
+  </si>
+  <si>
+    <t>Ветчина Нежная ТМ Особый рецепт полиамид ф/в 0,4 кг СК1</t>
+  </si>
+  <si>
+    <t>Сосиски Баварские с сыром ТМ Стародворье айпил мгс ф/в 0,35 кг СК4</t>
+  </si>
+  <si>
+    <t>Сосиски Ганноверские ТМ Стародворье амицел мгс ф/в 0,5 кг СК4</t>
+  </si>
+  <si>
+    <t>Сосиски Молокуши миникушай ТМ Вязанка амицел мгс ф/в 0,33 кг УВС СК3</t>
+  </si>
+  <si>
+    <t>Сосиски Вязанка Молочные ТМ Вязанка амицел мгс ф/в 0,45 кг УВС НД СК3</t>
+  </si>
+  <si>
+    <t>Сосиски Молочные для завтрака ТМ Особый рецепт полиамид мгс ф/в 0,4 кг НД2 СК3</t>
+  </si>
+  <si>
+    <t>P005198</t>
+  </si>
+  <si>
+    <t>Сосиски «Молочные для завтрака» Фикс.вес 0,4 п/а ТМ «Особый рецепт»</t>
+  </si>
+  <si>
+    <t>Сосиски Вязанка Сливочные ТМ Вязанка амицел мгс ф/в 0,33 кг УВС НД СК3</t>
+  </si>
+  <si>
+    <t>Сосиски Вязанка Сливочные ТМ Вязанка амицел мгс ф/в 0,45 кг УВС НД СК3</t>
+  </si>
+  <si>
+    <t>Сосиски Сочинки Молочные ТМ Стародворье амицел мгс ф/в 0,4 кг СК4</t>
+  </si>
+  <si>
+    <t>Сосиски Сочинки по-баварски ТМ Стародворье полиамид мгс ф/в 0,4 кг СК3</t>
+  </si>
+  <si>
+    <t>Сосиски Сочинки ТМ Стародворье с сочной грудинкой полиамид мгс ф/в 0,4 кг УВС НД СК4</t>
+  </si>
+  <si>
+    <t>Сосиски Сочинки ТМ Стародворье с сочным окороком полиамид мгс ф/в 0,4 кг УВС НД СК4</t>
+  </si>
+  <si>
+    <t>Сосиски Сочинки Сливочные ТМ Стародворье амицел мгс ф/в 0,4 кг СК3</t>
+  </si>
+  <si>
+    <t>Сосиски «Сочинки Сливочные» Фикс.вес 0,4 п/а мгс ТМ «Стародворье»</t>
+  </si>
+  <si>
+    <t>Сардельки Сочинки ТМ Стародворье полиамид мгс ф/в 0,4 кг НД СК4</t>
+  </si>
+  <si>
+    <t>Сардельки «Сочинки» Фикс.вес 0,4 п/а ТМ «Стародворье»</t>
+  </si>
+  <si>
+    <t>Колбаса сырокопченая Сальчичон ТМ Стародворье в/у ф/в 0,07 кг нарезка Топ-ЛКК, Дистр МЗР</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Колбаса сырокопченая Сервелат Ореховый ТМ Стародворье в/у ф/в 0,07 кг нарезка Топ-ЛКК, Дистр МЗР</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Колбаса сыровяленая Фуэт ТМ Стародворье в/у ф/в 0,07 кг нарезка Топ-ЛКК, Дистр МЗР</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Паштет печеночный Со сливочным маслом ТМ Стародворье ламистер ф/в 0,1 кг РК</t>
   </si>
 </sst>
 </file>
@@ -10276,7 +10417,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G2364"/>
+  <dimension ref="A1:G2407"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="86.140625" style="7" customWidth="1"/>
@@ -60571,8 +60712,997 @@
         <v>3223</v>
       </c>
     </row>
+    <row r="2365" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A2365" s="40" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B2365" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2365" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2365" s="42">
+        <v>4301031199</v>
+      </c>
+      <c r="E2365" s="41">
+        <v>4680115880986</v>
+      </c>
+      <c r="F2365" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="G2365" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2366" s="40" t="s">
+        <v>3225</v>
+      </c>
+      <c r="B2366" s="41" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C2366" s="41" t="s">
+        <v>2576</v>
+      </c>
+      <c r="D2366" s="42">
+        <v>4301031419</v>
+      </c>
+      <c r="E2366" s="41">
+        <v>4680115882072</v>
+      </c>
+      <c r="F2366" s="43" t="s">
+        <v>2577</v>
+      </c>
+      <c r="G2366" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2367" s="40" t="s">
+        <v>3226</v>
+      </c>
+      <c r="B2367" s="41" t="s">
+        <v>414</v>
+      </c>
+      <c r="C2367" s="41" t="s">
+        <v>3017</v>
+      </c>
+      <c r="D2367" s="42">
+        <v>4301031418</v>
+      </c>
+      <c r="E2367" s="41">
+        <v>4680115882102</v>
+      </c>
+      <c r="F2367" s="43" t="s">
+        <v>3018</v>
+      </c>
+      <c r="G2367" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2368" s="40" t="s">
+        <v>3227</v>
+      </c>
+      <c r="B2368" s="41" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2368" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D2368" s="42">
+        <v>4301031205</v>
+      </c>
+      <c r="E2368" s="41">
+        <v>4680115881785</v>
+      </c>
+      <c r="F2368" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="G2368" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2369" s="40" t="s">
+        <v>3228</v>
+      </c>
+      <c r="B2369" s="41" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2369" s="41" t="s">
+        <v>2588</v>
+      </c>
+      <c r="D2369" s="42">
+        <v>4301031362</v>
+      </c>
+      <c r="E2369" s="41">
+        <v>4607091384338</v>
+      </c>
+      <c r="F2369" s="43" t="s">
+        <v>373</v>
+      </c>
+      <c r="G2369" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2370" s="40" t="s">
+        <v>3229</v>
+      </c>
+      <c r="B2370" s="41" t="s">
+        <v>415</v>
+      </c>
+      <c r="C2370" s="41" t="s">
+        <v>3019</v>
+      </c>
+      <c r="D2370" s="42">
+        <v>4301031417</v>
+      </c>
+      <c r="E2370" s="41">
+        <v>4680115882096</v>
+      </c>
+      <c r="F2370" s="43" t="s">
+        <v>3020</v>
+      </c>
+      <c r="G2370" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2371" s="40" t="s">
+        <v>3230</v>
+      </c>
+      <c r="B2371" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2371" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="D2371" s="42">
+        <v>4301031201</v>
+      </c>
+      <c r="E2371" s="41">
+        <v>4680115881563</v>
+      </c>
+      <c r="F2371" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="G2371" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2372" s="40" t="s">
+        <v>3231</v>
+      </c>
+      <c r="B2372" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2372" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2372" s="42">
+        <v>4301031202</v>
+      </c>
+      <c r="E2372" s="41">
+        <v>4680115881679</v>
+      </c>
+      <c r="F2372" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="G2372" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2373" s="40" t="s">
+        <v>3232</v>
+      </c>
+      <c r="B2373" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2373" s="41" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D2373" s="42">
+        <v>4301031305</v>
+      </c>
+      <c r="E2373" s="41">
+        <v>4607091389845</v>
+      </c>
+      <c r="F2373" s="43" t="s">
+        <v>208</v>
+      </c>
+      <c r="G2373" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2374" s="40" t="s">
+        <v>3233</v>
+      </c>
+      <c r="B2374" s="41" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C2374" s="41" t="s">
+        <v>2401</v>
+      </c>
+      <c r="D2374" s="42">
+        <v>4301031223</v>
+      </c>
+      <c r="E2374" s="41">
+        <v>4680115884014</v>
+      </c>
+      <c r="F2374" s="43" t="s">
+        <v>2402</v>
+      </c>
+      <c r="G2374" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2375" s="40" t="s">
+        <v>3234</v>
+      </c>
+      <c r="B2375" s="41" t="s">
+        <v>2404</v>
+      </c>
+      <c r="C2375" s="41" t="s">
+        <v>2405</v>
+      </c>
+      <c r="D2375" s="42">
+        <v>4301031222</v>
+      </c>
+      <c r="E2375" s="41">
+        <v>4680115884007</v>
+      </c>
+      <c r="F2375" s="43" t="s">
+        <v>2406</v>
+      </c>
+      <c r="G2375" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2376" s="40" t="s">
+        <v>3235</v>
+      </c>
+      <c r="B2376" s="41" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2376" s="41" t="s">
+        <v>312</v>
+      </c>
+      <c r="D2376" s="42">
+        <v>4301031066</v>
+      </c>
+      <c r="E2376" s="41">
+        <v>4607091383836</v>
+      </c>
+      <c r="F2376" s="43" t="s">
+        <v>314</v>
+      </c>
+      <c r="G2376" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2377" s="40" t="s">
+        <v>3236</v>
+      </c>
+      <c r="B2377" s="41" t="s">
+        <v>657</v>
+      </c>
+      <c r="C2377" s="41" t="s">
+        <v>658</v>
+      </c>
+      <c r="D2377" s="42">
+        <v>4301031220</v>
+      </c>
+      <c r="E2377" s="41">
+        <v>4680115882669</v>
+      </c>
+      <c r="F2377" s="43" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G2377" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2378" s="40" t="s">
+        <v>3237</v>
+      </c>
+      <c r="B2378" s="41" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C2378" s="41" t="s">
+        <v>3176</v>
+      </c>
+      <c r="D2378" s="42">
+        <v>4301012035</v>
+      </c>
+      <c r="E2378" s="41">
+        <v>4680115880603</v>
+      </c>
+      <c r="F2378" s="43" t="s">
+        <v>3177</v>
+      </c>
+      <c r="G2378" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2379" s="40" t="s">
+        <v>3238</v>
+      </c>
+      <c r="B2379" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2379" s="41" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D2379" s="42">
+        <v>4301011705</v>
+      </c>
+      <c r="E2379" s="41">
+        <v>4607091384604</v>
+      </c>
+      <c r="F2379" s="43" t="s">
+        <v>1895</v>
+      </c>
+      <c r="G2379" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2380" s="40" t="s">
+        <v>3239</v>
+      </c>
+      <c r="B2380" s="41" t="s">
+        <v>2466</v>
+      </c>
+      <c r="C2380" s="41" t="s">
+        <v>2467</v>
+      </c>
+      <c r="D2380" s="42">
+        <v>4301011443</v>
+      </c>
+      <c r="E2380" s="41">
+        <v>4680115881303</v>
+      </c>
+      <c r="F2380" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2380" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2381" s="40" t="s">
+        <v>3240</v>
+      </c>
+      <c r="B2381" s="41" t="s">
+        <v>2157</v>
+      </c>
+      <c r="C2381" s="41" t="s">
+        <v>2158</v>
+      </c>
+      <c r="D2381" s="42">
+        <v>4301011855</v>
+      </c>
+      <c r="E2381" s="41">
+        <v>4680115885837</v>
+      </c>
+      <c r="F2381" s="43" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G2381" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2382" s="40" t="s">
+        <v>3241</v>
+      </c>
+      <c r="B2382" s="41" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C2382" s="41" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D2382" s="42">
+        <v>4301012024</v>
+      </c>
+      <c r="E2382" s="41">
+        <v>4680115885615</v>
+      </c>
+      <c r="F2382" s="43" t="s">
+        <v>2099</v>
+      </c>
+      <c r="G2382" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2383" s="40" t="s">
+        <v>3242</v>
+      </c>
+      <c r="B2383" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2383" s="41" t="s">
+        <v>2743</v>
+      </c>
+      <c r="D2383" s="42">
+        <v>4301011514</v>
+      </c>
+      <c r="E2383" s="41">
+        <v>4680115882133</v>
+      </c>
+      <c r="F2383" s="43" t="s">
+        <v>1482</v>
+      </c>
+      <c r="G2383" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2384" s="40" t="s">
+        <v>3243</v>
+      </c>
+      <c r="B2384" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2384" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2384" s="42">
+        <v>4301011417</v>
+      </c>
+      <c r="E2384" s="41">
+        <v>4680115880269</v>
+      </c>
+      <c r="F2384" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2384" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2385" s="40" t="s">
+        <v>3244</v>
+      </c>
+      <c r="B2385" s="41" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C2385" s="41" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D2385" s="42">
+        <v>4301011415</v>
+      </c>
+      <c r="E2385" s="41">
+        <v>4680115880429</v>
+      </c>
+      <c r="F2385" s="43" t="s">
+        <v>2276</v>
+      </c>
+      <c r="G2385" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2386" s="40" t="s">
+        <v>3245</v>
+      </c>
+      <c r="B2386" s="41" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C2386" s="41" t="s">
+        <v>2165</v>
+      </c>
+      <c r="D2386" s="42">
+        <v>4301011858</v>
+      </c>
+      <c r="E2386" s="41">
+        <v>4680115885646</v>
+      </c>
+      <c r="F2386" s="43" t="s">
+        <v>2166</v>
+      </c>
+      <c r="G2386" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2387" s="40" t="s">
+        <v>3246</v>
+      </c>
+      <c r="B2387" s="41" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C2387" s="41" t="s">
+        <v>2154</v>
+      </c>
+      <c r="D2387" s="42">
+        <v>4301011850</v>
+      </c>
+      <c r="E2387" s="41">
+        <v>4680115885806</v>
+      </c>
+      <c r="F2387" s="43" t="s">
+        <v>2155</v>
+      </c>
+      <c r="G2387" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2388" s="40" t="s">
+        <v>3247</v>
+      </c>
+      <c r="B2388" s="41" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C2388" s="41" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D2388" s="42">
+        <v>4301011868</v>
+      </c>
+      <c r="E2388" s="41">
+        <v>4680115884861</v>
+      </c>
+      <c r="F2388" s="43" t="s">
+        <v>2129</v>
+      </c>
+      <c r="G2388" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2389" s="40" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B2389" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2389" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2389" s="42">
+        <v>4301011801</v>
+      </c>
+      <c r="E2389" s="41">
+        <v>4680115881419</v>
+      </c>
+      <c r="F2389" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2389" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2390" s="40" t="s">
+        <v>3249</v>
+      </c>
+      <c r="B2390" s="41" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2390" s="41" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2390" s="42">
+        <v>4301020179</v>
+      </c>
+      <c r="E2390" s="41">
+        <v>4607091384178</v>
+      </c>
+      <c r="F2390" s="43" t="s">
+        <v>335</v>
+      </c>
+      <c r="G2390" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2391" s="40" t="s">
+        <v>3250</v>
+      </c>
+      <c r="B2391" s="41" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C2391" s="41" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D2391" s="42">
+        <v>4301051864</v>
+      </c>
+      <c r="E2391" s="41">
+        <v>4680115883567</v>
+      </c>
+      <c r="F2391" s="43" t="s">
+        <v>1480</v>
+      </c>
+      <c r="G2391" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2392" s="40" t="s">
+        <v>3251</v>
+      </c>
+      <c r="B2392" s="41" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C2392" s="41" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D2392" s="42">
+        <v>4301051734</v>
+      </c>
+      <c r="E2392" s="41">
+        <v>4680115884588</v>
+      </c>
+      <c r="F2392" s="43" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G2392" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2393" s="40" t="s">
+        <v>3252</v>
+      </c>
+      <c r="B2393" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2393" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2393" s="42">
+        <v>4301051438</v>
+      </c>
+      <c r="E2393" s="41">
+        <v>4680115880894</v>
+      </c>
+      <c r="F2393" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="G2393" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2394" s="40" t="s">
+        <v>3253</v>
+      </c>
+      <c r="B2394" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2394" s="41" t="s">
+        <v>3058</v>
+      </c>
+      <c r="D2394" s="42">
+        <v>4301051718</v>
+      </c>
+      <c r="E2394" s="41">
+        <v>4607091385731</v>
+      </c>
+      <c r="F2394" s="43" t="s">
+        <v>3059</v>
+      </c>
+      <c r="G2394" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2395" s="40" t="s">
+        <v>3254</v>
+      </c>
+      <c r="B2395" s="41" t="s">
+        <v>354</v>
+      </c>
+      <c r="C2395" s="41" t="s">
+        <v>3255</v>
+      </c>
+      <c r="D2395" s="42">
+        <v>4301052069</v>
+      </c>
+      <c r="E2395" s="41">
+        <v>4607091384253</v>
+      </c>
+      <c r="F2395" s="43" t="s">
+        <v>3256</v>
+      </c>
+      <c r="G2395" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2396" s="40" t="s">
+        <v>3257</v>
+      </c>
+      <c r="B2396" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2396" s="41" t="s">
+        <v>2985</v>
+      </c>
+      <c r="D2396" s="42">
+        <v>4301051730</v>
+      </c>
+      <c r="E2396" s="41">
+        <v>4607091383256</v>
+      </c>
+      <c r="F2396" s="43" t="s">
+        <v>2986</v>
+      </c>
+      <c r="G2396" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2397" s="40" t="s">
+        <v>3258</v>
+      </c>
+      <c r="B2397" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2397" s="41" t="s">
+        <v>2787</v>
+      </c>
+      <c r="D2397" s="42">
+        <v>4301051721</v>
+      </c>
+      <c r="E2397" s="41">
+        <v>4607091385748</v>
+      </c>
+      <c r="F2397" s="43" t="s">
+        <v>2788</v>
+      </c>
+      <c r="G2397" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2398" s="40" t="s">
+        <v>3259</v>
+      </c>
+      <c r="B2398" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="C2398" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2398" s="42">
+        <v>4301051407</v>
+      </c>
+      <c r="E2398" s="41">
+        <v>4680115882195</v>
+      </c>
+      <c r="F2398" s="43" t="s">
+        <v>3063</v>
+      </c>
+      <c r="G2398" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2399" s="40" t="s">
+        <v>3260</v>
+      </c>
+      <c r="B2399" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2399" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="D2399" s="42">
+        <v>4301051388</v>
+      </c>
+      <c r="E2399" s="41">
+        <v>4680115881211</v>
+      </c>
+      <c r="F2399" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="G2399" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2400" s="40" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B2400" s="41" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2400" s="41" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D2400" s="42">
+        <v>4301051666</v>
+      </c>
+      <c r="E2400" s="41">
+        <v>4680115880092</v>
+      </c>
+      <c r="F2400" s="43" t="s">
+        <v>2062</v>
+      </c>
+      <c r="G2400" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2401" s="40" t="s">
+        <v>3262</v>
+      </c>
+      <c r="B2401" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2401" s="41" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D2401" s="42">
+        <v>4301051668</v>
+      </c>
+      <c r="E2401" s="41">
+        <v>4680115880221</v>
+      </c>
+      <c r="F2401" s="43" t="s">
+        <v>2064</v>
+      </c>
+      <c r="G2401" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2402" s="40" t="s">
+        <v>3263</v>
+      </c>
+      <c r="B2402" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2402" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2402" s="42">
+        <v>4301051410</v>
+      </c>
+      <c r="E2402" s="41">
+        <v>4680115882164</v>
+      </c>
+      <c r="F2402" s="43" t="s">
+        <v>3264</v>
+      </c>
+      <c r="G2402" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2403" s="40" t="s">
+        <v>3265</v>
+      </c>
+      <c r="B2403" s="41" t="s">
+        <v>265</v>
+      </c>
+      <c r="C2403" s="41" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D2403" s="42">
+        <v>4301060389</v>
+      </c>
+      <c r="E2403" s="41">
+        <v>4680115880801</v>
+      </c>
+      <c r="F2403" s="43" t="s">
+        <v>3266</v>
+      </c>
+      <c r="G2403" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2404" s="40" t="s">
+        <v>3267</v>
+      </c>
+      <c r="B2404" s="41" t="s">
+        <v>3000</v>
+      </c>
+      <c r="C2404" s="41" t="s">
+        <v>3001</v>
+      </c>
+      <c r="D2404" s="42">
+        <v>4301032051</v>
+      </c>
+      <c r="E2404" s="41">
+        <v>4680115886742</v>
+      </c>
+      <c r="F2404" s="43" t="s">
+        <v>3002</v>
+      </c>
+      <c r="G2404" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2405" s="40" t="s">
+        <v>3268</v>
+      </c>
+      <c r="B2405" s="41" t="s">
+        <v>3004</v>
+      </c>
+      <c r="C2405" s="41" t="s">
+        <v>3005</v>
+      </c>
+      <c r="D2405" s="42">
+        <v>4301032052</v>
+      </c>
+      <c r="E2405" s="41">
+        <v>4680115886766</v>
+      </c>
+      <c r="F2405" s="43" t="s">
+        <v>3006</v>
+      </c>
+      <c r="G2405" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2406" s="40" t="s">
+        <v>3269</v>
+      </c>
+      <c r="B2406" s="41" t="s">
+        <v>2988</v>
+      </c>
+      <c r="C2406" s="41" t="s">
+        <v>2989</v>
+      </c>
+      <c r="D2406" s="42">
+        <v>4301170013</v>
+      </c>
+      <c r="E2406" s="41">
+        <v>4680115886797</v>
+      </c>
+      <c r="F2406" s="43" t="s">
+        <v>2990</v>
+      </c>
+      <c r="G2406" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2407" s="40" t="s">
+        <v>3270</v>
+      </c>
+      <c r="B2407" s="41" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2407" s="41" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2407" s="42">
+        <v>4301180001</v>
+      </c>
+      <c r="E2407" s="41">
+        <v>4680115880016</v>
+      </c>
+      <c r="F2407" s="43" t="s">
+        <v>291</v>
+      </c>
+      <c r="G2407" s="44" t="s">
+        <v>3223</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2364" xr:uid="{569F81D0-594B-46FB-B57B-6536A980B8CA}"/>
+  <autoFilter ref="A1:G2407" xr:uid="{569F81D0-594B-46FB-B57B-6536A980B8CA}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>

--- a/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\ПОКОМ КИ\pokom_ki\WholesaleCustomers\moduls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\в бланки заводов\ПОКОМ КИ\pokom_ki\WholesaleCustomers\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77EFF568-2D41-4680-935E-0795B87F7BF1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34252CD5-44B7-4129-B1EB-B63B8B5714FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,25 +16,19 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$G$2407</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$G$2433</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9991" uniqueCount="3271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10121" uniqueCount="3299">
   <si>
     <t>SU002447</t>
   </si>
@@ -9847,6 +9841,90 @@
   </si>
   <si>
     <t xml:space="preserve"> Паштет печеночный Со сливочным маслом ТМ Стародворье ламистер ф/в 0,1 кг РК</t>
+  </si>
+  <si>
+    <t>Колбаса Филейская со шпиком ТМ Вязанка в оболочке полиамид.</t>
+  </si>
+  <si>
+    <t>Колбаса Филейная ТМ Особый рецепт ВЕС большой батон</t>
+  </si>
+  <si>
+    <t>Колбаса Молочная ТМ Особый рецепт ВЕС большой батон</t>
+  </si>
+  <si>
+    <t>Вареные колбасы «Молочная» Весовой п/а ТМ «Особый рецепт»</t>
+  </si>
+  <si>
+    <t>Колбаса Со шпиком ВЕС большой батон ТМ Особый рецепт</t>
+  </si>
+  <si>
+    <t>Колбаса Дугушка Стародворская ВЕС ТС Дугушка</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Молокуша ТМ Вязанка ВЕС,</t>
+  </si>
+  <si>
+    <t>Колбаса Докторская ГОСТ, Вязанка вектор,ВЕС. , кг</t>
+  </si>
+  <si>
+    <t>Колбаса Сливушка ТМ Вязанка. ВЕС.</t>
+  </si>
+  <si>
+    <t>Колбаса Сочинка по-европейски с сочной грудинкой ТМ Стародворье, ВЕС</t>
+  </si>
+  <si>
+    <t>Колбаса Сочинка по-фински с сочным окроком ТМ Стародворье ВЕС</t>
+  </si>
+  <si>
+    <t>Колбаса Сочинка рубленая с сочным окороком ТМ Стародворье ВЕС</t>
+  </si>
+  <si>
+    <t>Сосиски Вязанка Сливочные, Вязанка амицел ВЕС., кг</t>
+  </si>
+  <si>
+    <t>Ветчина Дугушка ТМ Стародворье, вектор в/у</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Филейская ТМ Вязанка ТС Классическая ВЕС</t>
+  </si>
+  <si>
+    <t>Ветчина Нежная ТМ Особый рецепт, (2,5кг), , кг</t>
+  </si>
+  <si>
+    <t>Колбаса Докторская ГОСТ Дугушка, ВЕС, ТМ Стародворье</t>
+  </si>
+  <si>
+    <t>Колбаса Молочная Дугушка, в/у, ВЕС, ТМ Стародворье</t>
+  </si>
+  <si>
+    <t>Колбаса Мясорубская с рубленой грудинкой ВЕС ТМ Стародворье  , кг</t>
+  </si>
+  <si>
+    <t>Колбаса Рубленая ЗАПЕЧ. Дугушка ТМ Стародворье, вектор, в/к</t>
+  </si>
+  <si>
+    <t>Колбаса Салями запеч Дугушка, оболочка вектор, ВЕС, ТМ Стародворье</t>
+  </si>
+  <si>
+    <t>Колбаса Сервелат ЗАПЕЧ.Дугушка ТМ Стародворье, вектор, в/к</t>
+  </si>
+  <si>
+    <t>Сардельки стародворские с говядиной в обол. , ВЕС.</t>
+  </si>
+  <si>
+    <t>Сосиски Вязанка Сливочные, Вязанка амицел МГС, 0.45кг, , шт</t>
+  </si>
+  <si>
+    <t>Сосиски Молочные для завтрака ТМ Особый рецепт, 0,4кг</t>
+  </si>
+  <si>
+    <t>Сосиски Сочинки с сочной грудинкой, МГС 0.4кг,</t>
+  </si>
+  <si>
+    <t>Пенза</t>
+  </si>
+  <si>
+    <t>Сосиски Вязанка Молочные, Вязанка вискофан  ВЕС., кг</t>
   </si>
 </sst>
 </file>
@@ -9906,7 +9984,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9946,6 +10024,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -10019,7 +10103,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -10131,6 +10215,19 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10417,7 +10514,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G2407"/>
+  <dimension ref="A1:G2433"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="86.140625" style="7" customWidth="1"/>
@@ -61701,8 +61798,606 @@
         <v>3223</v>
       </c>
     </row>
+    <row r="2408" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2408" s="45" t="s">
+        <v>3271</v>
+      </c>
+      <c r="B2408" s="46" t="s">
+        <v>2640</v>
+      </c>
+      <c r="C2408" s="46" t="s">
+        <v>2641</v>
+      </c>
+      <c r="D2408" s="47">
+        <v>4301012030</v>
+      </c>
+      <c r="E2408" s="46">
+        <v>4680115885882</v>
+      </c>
+      <c r="F2408" s="48" t="s">
+        <v>2642</v>
+      </c>
+      <c r="G2408" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2409" s="45" t="s">
+        <v>3272</v>
+      </c>
+      <c r="B2409" s="46" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C2409" s="46" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D2409" s="47">
+        <v>4301011867</v>
+      </c>
+      <c r="E2409" s="46">
+        <v>4680115884830</v>
+      </c>
+      <c r="F2409" s="48" t="s">
+        <v>2072</v>
+      </c>
+      <c r="G2409" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2410" s="45" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B2410" s="46" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C2410" s="46" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D2410" s="47">
+        <v>4301011869</v>
+      </c>
+      <c r="E2410" s="46">
+        <v>4680115884847</v>
+      </c>
+      <c r="F2410" s="48" t="s">
+        <v>3274</v>
+      </c>
+      <c r="G2410" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2411" s="45" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B2411" s="46" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C2411" s="46" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D2411" s="47">
+        <v>4301011870</v>
+      </c>
+      <c r="E2411" s="46">
+        <v>4680115884854</v>
+      </c>
+      <c r="F2411" s="48" t="s">
+        <v>1941</v>
+      </c>
+      <c r="G2411" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2412" s="45" t="s">
+        <v>3276</v>
+      </c>
+      <c r="B2412" s="46" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C2412" s="46" t="s">
+        <v>2123</v>
+      </c>
+      <c r="D2412" s="47">
+        <v>4301011376</v>
+      </c>
+      <c r="E2412" s="46">
+        <v>4680115885226</v>
+      </c>
+      <c r="F2412" s="48" t="s">
+        <v>2124</v>
+      </c>
+      <c r="G2412" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2413" s="45" t="s">
+        <v>3277</v>
+      </c>
+      <c r="B2413" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2413" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2413" s="47">
+        <v>4301011468</v>
+      </c>
+      <c r="E2413" s="46">
+        <v>4680115881327</v>
+      </c>
+      <c r="F2413" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2413" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2414" s="45" t="s">
+        <v>3278</v>
+      </c>
+      <c r="B2414" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2414" s="46" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D2414" s="47">
+        <v>4301011380</v>
+      </c>
+      <c r="E2414" s="46">
+        <v>4607091385670</v>
+      </c>
+      <c r="F2414" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2414" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2415" s="45" t="s">
+        <v>3279</v>
+      </c>
+      <c r="B2415" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2415" s="46" t="s">
+        <v>2743</v>
+      </c>
+      <c r="D2415" s="47">
+        <v>4301011514</v>
+      </c>
+      <c r="E2415" s="46">
+        <v>4680115882133</v>
+      </c>
+      <c r="F2415" s="48" t="s">
+        <v>1482</v>
+      </c>
+      <c r="G2415" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2416" s="45" t="s">
+        <v>3280</v>
+      </c>
+      <c r="B2416" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2416" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2416" s="47">
+        <v>4301031224</v>
+      </c>
+      <c r="E2416" s="46">
+        <v>4680115882683</v>
+      </c>
+      <c r="F2416" s="48" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G2416" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2417" s="45" t="s">
+        <v>3281</v>
+      </c>
+      <c r="B2417" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2417" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2417" s="47">
+        <v>4301031230</v>
+      </c>
+      <c r="E2417" s="46">
+        <v>4680115882690</v>
+      </c>
+      <c r="F2417" s="48" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G2417" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2418" s="45" t="s">
+        <v>3282</v>
+      </c>
+      <c r="B2418" s="46" t="s">
+        <v>661</v>
+      </c>
+      <c r="C2418" s="46" t="s">
+        <v>662</v>
+      </c>
+      <c r="D2418" s="47">
+        <v>4301031221</v>
+      </c>
+      <c r="E2418" s="46">
+        <v>4680115882676</v>
+      </c>
+      <c r="F2418" s="48" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G2418" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2419" s="45" t="s">
+        <v>3283</v>
+      </c>
+      <c r="B2419" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2419" s="46" t="s">
+        <v>2853</v>
+      </c>
+      <c r="D2419" s="47">
+        <v>4301051724</v>
+      </c>
+      <c r="E2419" s="46">
+        <v>4607091385168</v>
+      </c>
+      <c r="F2419" s="48" t="s">
+        <v>2854</v>
+      </c>
+      <c r="G2419" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2420" s="45" t="s">
+        <v>3284</v>
+      </c>
+      <c r="B2420" s="46" t="s">
+        <v>412</v>
+      </c>
+      <c r="C2420" s="46" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D2420" s="47">
+        <v>4301020334</v>
+      </c>
+      <c r="E2420" s="46">
+        <v>4607091388930</v>
+      </c>
+      <c r="F2420" s="48" t="s">
+        <v>413</v>
+      </c>
+      <c r="G2420" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2421" s="45" t="s">
+        <v>3285</v>
+      </c>
+      <c r="B2421" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2421" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2421" s="47">
+        <v>4301011816</v>
+      </c>
+      <c r="E2421" s="46">
+        <v>4680115881426</v>
+      </c>
+      <c r="F2421" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2421" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2422" s="45" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B2422" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2422" s="46" t="s">
+        <v>2855</v>
+      </c>
+      <c r="D2422" s="47">
+        <v>4301051712</v>
+      </c>
+      <c r="E2422" s="46">
+        <v>4607091386967</v>
+      </c>
+      <c r="F2422" s="48" t="s">
+        <v>2856</v>
+      </c>
+      <c r="G2422" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2423" s="45" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B2423" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="C2423" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="D2423" s="47">
+        <v>4301020178</v>
+      </c>
+      <c r="E2423" s="46">
+        <v>4607091383980</v>
+      </c>
+      <c r="F2423" s="48" t="s">
+        <v>334</v>
+      </c>
+      <c r="G2423" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2424" s="45" t="s">
+        <v>3287</v>
+      </c>
+      <c r="B2424" s="46" t="s">
+        <v>401</v>
+      </c>
+      <c r="C2424" s="46" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D2424" s="47">
+        <v>4301011795</v>
+      </c>
+      <c r="E2424" s="46">
+        <v>4607091389067</v>
+      </c>
+      <c r="F2424" s="48" t="s">
+        <v>406</v>
+      </c>
+      <c r="G2424" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2425" s="45" t="s">
+        <v>3288</v>
+      </c>
+      <c r="B2425" s="46" t="s">
+        <v>403</v>
+      </c>
+      <c r="C2425" s="46" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D2425" s="47">
+        <v>4301011771</v>
+      </c>
+      <c r="E2425" s="46">
+        <v>4607091389104</v>
+      </c>
+      <c r="F2425" s="48" t="s">
+        <v>1815</v>
+      </c>
+      <c r="G2425" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2426" s="45" t="s">
+        <v>3289</v>
+      </c>
+      <c r="B2426" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2426" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2426" s="47">
+        <v>4301031191</v>
+      </c>
+      <c r="E2426" s="46">
+        <v>4680115880993</v>
+      </c>
+      <c r="F2426" s="48" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2426" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2427" s="45" t="s">
+        <v>3290</v>
+      </c>
+      <c r="B2427" s="46" t="s">
+        <v>416</v>
+      </c>
+      <c r="C2427" s="46" t="s">
+        <v>2572</v>
+      </c>
+      <c r="D2427" s="47">
+        <v>4301031349</v>
+      </c>
+      <c r="E2427" s="46">
+        <v>4680115883116</v>
+      </c>
+      <c r="F2427" s="48" t="s">
+        <v>2573</v>
+      </c>
+      <c r="G2427" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2428" s="45" t="s">
+        <v>3291</v>
+      </c>
+      <c r="B2428" s="46" t="s">
+        <v>417</v>
+      </c>
+      <c r="C2428" s="46" t="s">
+        <v>2636</v>
+      </c>
+      <c r="D2428" s="47">
+        <v>4301031350</v>
+      </c>
+      <c r="E2428" s="46">
+        <v>4680115883093</v>
+      </c>
+      <c r="F2428" s="48" t="s">
+        <v>2637</v>
+      </c>
+      <c r="G2428" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2429" s="45" t="s">
+        <v>3292</v>
+      </c>
+      <c r="B2429" s="46" t="s">
+        <v>418</v>
+      </c>
+      <c r="C2429" s="46" t="s">
+        <v>2638</v>
+      </c>
+      <c r="D2429" s="47">
+        <v>4301031353</v>
+      </c>
+      <c r="E2429" s="46">
+        <v>4680115883109</v>
+      </c>
+      <c r="F2429" s="48" t="s">
+        <v>2639</v>
+      </c>
+      <c r="G2429" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2430" s="45" t="s">
+        <v>3293</v>
+      </c>
+      <c r="B2430" s="46" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2430" s="46" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2430" s="47">
+        <v>4301060406</v>
+      </c>
+      <c r="E2430" s="46">
+        <v>4607091384482</v>
+      </c>
+      <c r="F2430" s="48" t="s">
+        <v>2646</v>
+      </c>
+      <c r="G2430" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2431" s="45" t="s">
+        <v>3294</v>
+      </c>
+      <c r="B2431" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2431" s="46" t="s">
+        <v>2787</v>
+      </c>
+      <c r="D2431" s="47">
+        <v>4301051721</v>
+      </c>
+      <c r="E2431" s="46">
+        <v>4607091385748</v>
+      </c>
+      <c r="F2431" s="48" t="s">
+        <v>2788</v>
+      </c>
+      <c r="G2431" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2432" s="45" t="s">
+        <v>3295</v>
+      </c>
+      <c r="B2432" s="46" t="s">
+        <v>354</v>
+      </c>
+      <c r="C2432" s="46" t="s">
+        <v>3255</v>
+      </c>
+      <c r="D2432" s="47">
+        <v>4301052069</v>
+      </c>
+      <c r="E2432" s="46">
+        <v>4607091384253</v>
+      </c>
+      <c r="F2432" s="48" t="s">
+        <v>3256</v>
+      </c>
+      <c r="G2432" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2433" s="45" t="s">
+        <v>3296</v>
+      </c>
+      <c r="B2433" s="46" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2433" s="46" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D2433" s="47">
+        <v>4301051666</v>
+      </c>
+      <c r="E2433" s="46">
+        <v>4680115880092</v>
+      </c>
+      <c r="F2433" s="48" t="s">
+        <v>2062</v>
+      </c>
+      <c r="G2433" s="49" t="s">
+        <v>3297</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2407" xr:uid="{569F81D0-594B-46FB-B57B-6536A980B8CA}"/>
+  <autoFilter ref="A1:G2433" xr:uid="{569F81D0-594B-46FB-B57B-6536A980B8CA}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>

--- a/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\ПОКОМ КИ\pokom_ki\WholesaleCustomers\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD87911-C153-444B-9B41-3B32E6FCB4B7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B3DC6B-B256-486F-93B5-17B0F0DBFFD6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10137" uniqueCount="3303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10157" uniqueCount="3308">
   <si>
     <t>SU002447</t>
   </si>
@@ -9943,6 +9943,21 @@
   </si>
   <si>
     <t>Сосиски Баварские 350гр ТМ Стародворье (1/6шт) Стародворье</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТ Ветчина Сливушка с ИНДЕЙКОЙ 400 гр ШТ Стародворье </t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТ Особая 0,5 Зареченские Славница 1/10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТ Мусульманская «Аль-Ислами халяль» ф/в 0,35 фиброуз ТМ «Вязанка» 1/8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТ СОСИСКИ СОЧИНКИ с сыром 0,4 Стародворье </t>
+  </si>
+  <si>
+    <t>Пушкарный</t>
   </si>
 </sst>
 </file>
@@ -10532,7 +10547,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G2437"/>
+  <dimension ref="A1:G2441"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="86.140625" style="7" customWidth="1"/>
@@ -62498,6 +62513,98 @@
         <v>3297</v>
       </c>
     </row>
+    <row r="2438" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2438" s="35" t="s">
+        <v>3303</v>
+      </c>
+      <c r="B2438" s="36" t="s">
+        <v>2453</v>
+      </c>
+      <c r="C2438" s="36" t="s">
+        <v>2454</v>
+      </c>
+      <c r="D2438" s="37">
+        <v>4301020344</v>
+      </c>
+      <c r="E2438" s="36">
+        <v>4680115880658</v>
+      </c>
+      <c r="F2438" s="38" t="s">
+        <v>2384</v>
+      </c>
+      <c r="G2438" s="39" t="s">
+        <v>3307</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2439" s="35" t="s">
+        <v>3304</v>
+      </c>
+      <c r="B2439" s="36" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C2439" s="36" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D2439" s="37">
+        <v>4301011952</v>
+      </c>
+      <c r="E2439" s="36">
+        <v>4680115884922</v>
+      </c>
+      <c r="F2439" s="38" t="s">
+        <v>1963</v>
+      </c>
+      <c r="G2439" s="39" t="s">
+        <v>3307</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2440" s="35" t="s">
+        <v>3305</v>
+      </c>
+      <c r="B2440" s="36" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C2440" s="36" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D2440" s="37">
+        <v>4301031234</v>
+      </c>
+      <c r="E2440" s="36">
+        <v>4680115883444</v>
+      </c>
+      <c r="F2440" s="38" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G2440" s="39" t="s">
+        <v>3307</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2441" s="35" t="s">
+        <v>3306</v>
+      </c>
+      <c r="B2441" s="36" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2441" s="36" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D2441" s="37">
+        <v>4301051945</v>
+      </c>
+      <c r="E2441" s="36">
+        <v>4680115880504</v>
+      </c>
+      <c r="F2441" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="G2441" s="39" t="s">
+        <v>3307</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G2437" xr:uid="{569F81D0-594B-46FB-B57B-6536A980B8CA}"/>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\ПОКОМ КИ\pokom_ki\WholesaleCustomers\moduls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\в бланки заводов\ПОКОМ КИ\pokom_ki\WholesaleCustomers\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEFD1BB-52EE-4879-99BC-318A39865481}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B58D19A-36CA-49A5-8DCE-F2FC932E1487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,25 +16,19 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$G$2442</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$G$2453</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10161" uniqueCount="3309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10216" uniqueCount="3320">
   <si>
     <t>SU002447</t>
   </si>
@@ -9961,6 +9955,39 @@
   </si>
   <si>
     <t>Мини-салями со вкусом бекона,  0.05кг, ядрена копоть   ПОКОМ</t>
+  </si>
+  <si>
+    <t>Ветчина Филейская ВЕС ТМ  Вязанка ТС Столичная</t>
+  </si>
+  <si>
+    <t>Ветчина Филейская ТМ Вязанка Столичная 0,45 кг</t>
+  </si>
+  <si>
+    <t>Колбаса Докторская ГОСТ, Вязанка вектор, 0,4 кг, , шт</t>
+  </si>
+  <si>
+    <t>Колбаса Сочинка зернистая с сочной грудинкой ТМ Стародворье.ВЕС</t>
+  </si>
+  <si>
+    <t>Сардельки Сочные ТМ Особый рецепт,   , кг</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Молокуша 0,45кг ТМ Вязанка</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Филейская ТМ Вязанка ТС Классическая, 0,45 кг.</t>
+  </si>
+  <si>
+    <t>Колбаса Нежная ТМ Зареченские ВЕС</t>
+  </si>
+  <si>
+    <t>Сосиски Сочинки, ВЕС, ТМ Стародворье</t>
+  </si>
+  <si>
+    <t>Сосиски Датские ТМ Особый рецепт, ВЕС</t>
+  </si>
+  <si>
+    <t>колб Щвейцарская с/к</t>
   </si>
 </sst>
 </file>
@@ -10550,7 +10577,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G2442"/>
+  <dimension ref="A1:G2453"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="86.140625" style="7" customWidth="1"/>
@@ -62537,100 +62564,353 @@
         <v>3295</v>
       </c>
     </row>
-    <row r="2439" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2439" s="35" t="s">
+    <row r="2439" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2439" s="45" t="s">
+        <v>3309</v>
+      </c>
+      <c r="B2439" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2439" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2439" s="47">
+        <v>4301020298</v>
+      </c>
+      <c r="E2439" s="46">
+        <v>4680115881440</v>
+      </c>
+      <c r="F2439" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2439" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2440" s="45" t="s">
+        <v>3310</v>
+      </c>
+      <c r="B2440" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2440" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2440" s="47">
+        <v>4301020296</v>
+      </c>
+      <c r="E2440" s="46">
+        <v>4680115881433</v>
+      </c>
+      <c r="F2440" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2440" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2441" s="45" t="s">
+        <v>3311</v>
+      </c>
+      <c r="B2441" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2441" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2441" s="47">
+        <v>4301011382</v>
+      </c>
+      <c r="E2441" s="46">
+        <v>4607091385687</v>
+      </c>
+      <c r="F2441" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2441" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2442" s="45" t="s">
+        <v>3312</v>
+      </c>
+      <c r="B2442" s="46" t="s">
+        <v>657</v>
+      </c>
+      <c r="C2442" s="46" t="s">
+        <v>658</v>
+      </c>
+      <c r="D2442" s="47">
+        <v>4301031220</v>
+      </c>
+      <c r="E2442" s="46">
+        <v>4680115882669</v>
+      </c>
+      <c r="F2442" s="48" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G2442" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2443" s="45" t="s">
+        <v>3313</v>
+      </c>
+      <c r="B2443" s="46" t="s">
+        <v>341</v>
+      </c>
+      <c r="C2443" s="46" t="s">
+        <v>3045</v>
+      </c>
+      <c r="D2443" s="47">
+        <v>4301060524</v>
+      </c>
+      <c r="E2443" s="46">
+        <v>4607091384673</v>
+      </c>
+      <c r="F2443" s="48" t="s">
+        <v>2507</v>
+      </c>
+      <c r="G2443" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2444" s="45" t="s">
+        <v>3314</v>
+      </c>
+      <c r="B2444" s="46" t="s">
+        <v>2464</v>
+      </c>
+      <c r="C2444" s="46" t="s">
+        <v>2465</v>
+      </c>
+      <c r="D2444" s="47">
+        <v>4301011443</v>
+      </c>
+      <c r="E2444" s="46">
+        <v>4680115881303</v>
+      </c>
+      <c r="F2444" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2444" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2445" s="45" t="s">
+        <v>3315</v>
+      </c>
+      <c r="B2445" s="46" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2445" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2445" s="47">
+        <v>4301011801</v>
+      </c>
+      <c r="E2445" s="46">
+        <v>4680115881419</v>
+      </c>
+      <c r="F2445" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2445" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2446" s="45" t="s">
+        <v>3316</v>
+      </c>
+      <c r="B2446" s="46" t="s">
+        <v>428</v>
+      </c>
+      <c r="C2446" s="46" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D2446" s="47">
+        <v>4301011584</v>
+      </c>
+      <c r="E2446" s="46">
+        <v>4640242180564</v>
+      </c>
+      <c r="F2446" s="48" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G2446" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2447" s="45" t="s">
+        <v>3317</v>
+      </c>
+      <c r="B2447" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2447" s="46" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D2447" s="47">
+        <v>4301051656</v>
+      </c>
+      <c r="E2447" s="46">
+        <v>4680115880573</v>
+      </c>
+      <c r="F2447" s="48" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G2447" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2448" s="45" t="s">
+        <v>3318</v>
+      </c>
+      <c r="B2448" s="46" t="s">
+        <v>2754</v>
+      </c>
+      <c r="C2448" s="46" t="s">
+        <v>2755</v>
+      </c>
+      <c r="D2448" s="47">
+        <v>4301051903</v>
+      </c>
+      <c r="E2448" s="46">
+        <v>4607091383928</v>
+      </c>
+      <c r="F2448" s="48" t="s">
+        <v>2756</v>
+      </c>
+      <c r="G2448" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2449" s="45" t="s">
+        <v>3319</v>
+      </c>
+      <c r="B2449" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="C2449" s="46" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D2449" s="47">
+        <v>4301030233</v>
+      </c>
+      <c r="E2449" s="46">
+        <v>4607091388404</v>
+      </c>
+      <c r="F2449" s="48" t="s">
+        <v>279</v>
+      </c>
+      <c r="G2449" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2450" s="35" t="s">
         <v>3301</v>
       </c>
-      <c r="B2439" s="36" t="s">
+      <c r="B2450" s="36" t="s">
         <v>2451</v>
       </c>
-      <c r="C2439" s="36" t="s">
+      <c r="C2450" s="36" t="s">
         <v>2452</v>
       </c>
-      <c r="D2439" s="37">
+      <c r="D2450" s="37">
         <v>4301020344</v>
       </c>
-      <c r="E2439" s="36">
+      <c r="E2450" s="36">
         <v>4680115880658</v>
       </c>
-      <c r="F2439" s="38" t="s">
+      <c r="F2450" s="38" t="s">
         <v>2382</v>
       </c>
-      <c r="G2439" s="39" t="s">
+      <c r="G2450" s="39" t="s">
         <v>3305</v>
       </c>
     </row>
-    <row r="2440" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2440" s="35" t="s">
+    <row r="2451" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2451" s="35" t="s">
         <v>3302</v>
       </c>
-      <c r="B2440" s="36" t="s">
+      <c r="B2451" s="36" t="s">
         <v>1959</v>
       </c>
-      <c r="C2440" s="36" t="s">
+      <c r="C2451" s="36" t="s">
         <v>1960</v>
       </c>
-      <c r="D2440" s="37">
+      <c r="D2451" s="37">
         <v>4301011952</v>
       </c>
-      <c r="E2440" s="36">
+      <c r="E2451" s="36">
         <v>4680115884922</v>
       </c>
-      <c r="F2440" s="38" t="s">
+      <c r="F2451" s="38" t="s">
         <v>1961</v>
       </c>
-      <c r="G2440" s="39" t="s">
+      <c r="G2451" s="39" t="s">
         <v>3305</v>
       </c>
     </row>
-    <row r="2441" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2441" s="35" t="s">
+    <row r="2452" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2452" s="35" t="s">
         <v>3303</v>
       </c>
-      <c r="B2441" s="36" t="s">
+      <c r="B2452" s="36" t="s">
         <v>1173</v>
       </c>
-      <c r="C2441" s="36" t="s">
+      <c r="C2452" s="36" t="s">
         <v>1174</v>
       </c>
-      <c r="D2441" s="37">
+      <c r="D2452" s="37">
         <v>4301031234</v>
       </c>
-      <c r="E2441" s="36">
+      <c r="E2452" s="36">
         <v>4680115883444</v>
       </c>
-      <c r="F2441" s="38" t="s">
+      <c r="F2452" s="38" t="s">
         <v>1175</v>
       </c>
-      <c r="G2441" s="39" t="s">
+      <c r="G2452" s="39" t="s">
         <v>3305</v>
       </c>
     </row>
-    <row r="2442" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2442" s="35" t="s">
+    <row r="2453" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2453" s="35" t="s">
         <v>3304</v>
       </c>
-      <c r="B2442" s="36" t="s">
+      <c r="B2453" s="36" t="s">
         <v>241</v>
       </c>
-      <c r="C2442" s="36" t="s">
+      <c r="C2453" s="36" t="s">
         <v>1967</v>
       </c>
-      <c r="D2442" s="37">
+      <c r="D2453" s="37">
         <v>4301051945</v>
       </c>
-      <c r="E2442" s="36">
+      <c r="E2453" s="36">
         <v>4680115880504</v>
       </c>
-      <c r="F2442" s="38" t="s">
+      <c r="F2453" s="38" t="s">
         <v>259</v>
       </c>
-      <c r="G2442" s="39" t="s">
+      <c r="G2453" s="39" t="s">
         <v>3305</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2442" xr:uid="{569F81D0-594B-46FB-B57B-6536A980B8CA}"/>
+  <autoFilter ref="A1:G2453" xr:uid="{569F81D0-594B-46FB-B57B-6536A980B8CA}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>

--- a/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\в бланки заводов\ПОКОМ КИ\pokom_ki\WholesaleCustomers\moduls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\ПОКОМ КИ\pokom_ki\WholesaleCustomers\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B58D19A-36CA-49A5-8DCE-F2FC932E1487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1DE9D7-2039-49CC-B32A-FB42A4E7413F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$G$2453</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$G$2464</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10216" uniqueCount="3320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10271" uniqueCount="3331">
   <si>
     <t>SU002447</t>
   </si>
@@ -9988,6 +9988,39 @@
   </si>
   <si>
     <t>колб Щвейцарская с/к</t>
+  </si>
+  <si>
+    <t>Колбаса Филедворская по-стародворски ТМ Стародворье в оболочке полиамид.</t>
+  </si>
+  <si>
+    <t>Колбаса Салями Филейбургская зернистая, оболочка фиброуз, ВЕС, ТМ Баварушка</t>
+  </si>
+  <si>
+    <t>Колбаса Сервелат Зернистый, ВЕС.  , кг</t>
+  </si>
+  <si>
+    <t>Колбаса Филейбургская с сочным окороком, ВЕС, ТМ Баварушка  , кг</t>
+  </si>
+  <si>
+    <t>Сардельки Филейские Вязанка ВЕС  ТМ Вязанка</t>
+  </si>
+  <si>
+    <t>Колбаса Дугушка со шпиком, ВЕС, ТМ Стародворье</t>
+  </si>
+  <si>
+    <t>Колбаса Сервелат Мясорубский с мелкорубленным окороком в/у  ТМ Стародворье ВЕС</t>
+  </si>
+  <si>
+    <t>Колбаса Сервелат Столичный, Вязанка фиброуз в/у,</t>
+  </si>
+  <si>
+    <t>Сардельки Нежные, ВЕС.</t>
+  </si>
+  <si>
+    <t>Шпикачки Стародворские, ВЕС.</t>
+  </si>
+  <si>
+    <t>Сосиски Баварские с сыром ТМ Стародворье 0,35 кг.</t>
   </si>
 </sst>
 </file>
@@ -10577,7 +10610,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G2453"/>
+  <dimension ref="A1:G2464"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="86.140625" style="7" customWidth="1"/>
@@ -62818,99 +62851,352 @@
       </c>
     </row>
     <row r="2450" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2450" s="35" t="s">
+      <c r="A2450" s="45" t="s">
+        <v>3320</v>
+      </c>
+      <c r="B2450" s="46" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C2450" s="46" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D2450" s="47">
+        <v>4301011850</v>
+      </c>
+      <c r="E2450" s="46">
+        <v>4680115885806</v>
+      </c>
+      <c r="F2450" s="48" t="s">
+        <v>2153</v>
+      </c>
+      <c r="G2450" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2451" s="45" t="s">
+        <v>3321</v>
+      </c>
+      <c r="B2451" s="46" t="s">
+        <v>363</v>
+      </c>
+      <c r="C2451" s="46" t="s">
+        <v>2550</v>
+      </c>
+      <c r="D2451" s="47">
+        <v>4301031405</v>
+      </c>
+      <c r="E2451" s="46">
+        <v>4680115886100</v>
+      </c>
+      <c r="F2451" s="48" t="s">
+        <v>2551</v>
+      </c>
+      <c r="G2451" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2452" s="45" t="s">
+        <v>3322</v>
+      </c>
+      <c r="B2452" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2452" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="D2452" s="47">
+        <v>4301030878</v>
+      </c>
+      <c r="E2452" s="46">
+        <v>4607091387193</v>
+      </c>
+      <c r="F2452" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="G2452" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2453" s="45" t="s">
+        <v>3323</v>
+      </c>
+      <c r="B2453" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="C2453" s="46" t="s">
+        <v>2652</v>
+      </c>
+      <c r="D2453" s="47">
+        <v>4301031402</v>
+      </c>
+      <c r="E2453" s="46">
+        <v>4680115886124</v>
+      </c>
+      <c r="F2453" s="48" t="s">
+        <v>2653</v>
+      </c>
+      <c r="G2453" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2454" s="45" t="s">
+        <v>3324</v>
+      </c>
+      <c r="B2454" s="46" t="s">
+        <v>909</v>
+      </c>
+      <c r="C2454" s="46" t="s">
+        <v>2806</v>
+      </c>
+      <c r="D2454" s="47">
+        <v>4301060455</v>
+      </c>
+      <c r="E2454" s="46">
+        <v>4680115881532</v>
+      </c>
+      <c r="F2454" s="48" t="s">
+        <v>1628</v>
+      </c>
+      <c r="G2454" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2455" s="45" t="s">
+        <v>3325</v>
+      </c>
+      <c r="B2455" s="46" t="s">
+        <v>402</v>
+      </c>
+      <c r="C2455" s="46" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D2455" s="47">
+        <v>4301011961</v>
+      </c>
+      <c r="E2455" s="46">
+        <v>4680115885271</v>
+      </c>
+      <c r="F2455" s="48" t="s">
+        <v>2110</v>
+      </c>
+      <c r="G2455" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2456" s="45" t="s">
+        <v>3326</v>
+      </c>
+      <c r="B2456" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2456" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="D2456" s="47">
+        <v>4301031201</v>
+      </c>
+      <c r="E2456" s="46">
+        <v>4680115881563</v>
+      </c>
+      <c r="F2456" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="G2456" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2457" s="45" t="s">
+        <v>3327</v>
+      </c>
+      <c r="B2457" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2457" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2457" s="47">
+        <v>4301030963</v>
+      </c>
+      <c r="E2457" s="46">
+        <v>4607091382426</v>
+      </c>
+      <c r="F2457" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2457" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2458" s="45" t="s">
+        <v>3328</v>
+      </c>
+      <c r="B2458" s="46" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2458" s="46" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D2458" s="47">
+        <v>4301060387</v>
+      </c>
+      <c r="E2458" s="46">
+        <v>4607091380880</v>
+      </c>
+      <c r="F2458" s="48" t="s">
+        <v>2643</v>
+      </c>
+      <c r="G2458" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2459" s="45" t="s">
+        <v>3329</v>
+      </c>
+      <c r="B2459" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2459" s="46" t="s">
+        <v>2645</v>
+      </c>
+      <c r="D2459" s="47">
+        <v>4301060484</v>
+      </c>
+      <c r="E2459" s="46">
+        <v>4607091380897</v>
+      </c>
+      <c r="F2459" s="48" t="s">
+        <v>2646</v>
+      </c>
+      <c r="G2459" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2460" s="45" t="s">
+        <v>3330</v>
+      </c>
+      <c r="B2460" s="46" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C2460" s="46" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D2460" s="47">
+        <v>4301051864</v>
+      </c>
+      <c r="E2460" s="46">
+        <v>4680115883567</v>
+      </c>
+      <c r="F2460" s="48" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G2460" s="49" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2461" s="35" t="s">
         <v>3301</v>
       </c>
-      <c r="B2450" s="36" t="s">
+      <c r="B2461" s="36" t="s">
         <v>2451</v>
       </c>
-      <c r="C2450" s="36" t="s">
+      <c r="C2461" s="36" t="s">
         <v>2452</v>
       </c>
-      <c r="D2450" s="37">
+      <c r="D2461" s="37">
         <v>4301020344</v>
       </c>
-      <c r="E2450" s="36">
+      <c r="E2461" s="36">
         <v>4680115880658</v>
       </c>
-      <c r="F2450" s="38" t="s">
+      <c r="F2461" s="38" t="s">
         <v>2382</v>
       </c>
-      <c r="G2450" s="39" t="s">
+      <c r="G2461" s="39" t="s">
         <v>3305</v>
       </c>
     </row>
-    <row r="2451" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2451" s="35" t="s">
+    <row r="2462" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2462" s="35" t="s">
         <v>3302</v>
       </c>
-      <c r="B2451" s="36" t="s">
+      <c r="B2462" s="36" t="s">
         <v>1959</v>
       </c>
-      <c r="C2451" s="36" t="s">
+      <c r="C2462" s="36" t="s">
         <v>1960</v>
       </c>
-      <c r="D2451" s="37">
+      <c r="D2462" s="37">
         <v>4301011952</v>
       </c>
-      <c r="E2451" s="36">
+      <c r="E2462" s="36">
         <v>4680115884922</v>
       </c>
-      <c r="F2451" s="38" t="s">
+      <c r="F2462" s="38" t="s">
         <v>1961</v>
       </c>
-      <c r="G2451" s="39" t="s">
+      <c r="G2462" s="39" t="s">
         <v>3305</v>
       </c>
     </row>
-    <row r="2452" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2452" s="35" t="s">
+    <row r="2463" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2463" s="35" t="s">
         <v>3303</v>
       </c>
-      <c r="B2452" s="36" t="s">
+      <c r="B2463" s="36" t="s">
         <v>1173</v>
       </c>
-      <c r="C2452" s="36" t="s">
+      <c r="C2463" s="36" t="s">
         <v>1174</v>
       </c>
-      <c r="D2452" s="37">
+      <c r="D2463" s="37">
         <v>4301031234</v>
       </c>
-      <c r="E2452" s="36">
+      <c r="E2463" s="36">
         <v>4680115883444</v>
       </c>
-      <c r="F2452" s="38" t="s">
+      <c r="F2463" s="38" t="s">
         <v>1175</v>
       </c>
-      <c r="G2452" s="39" t="s">
+      <c r="G2463" s="39" t="s">
         <v>3305</v>
       </c>
     </row>
-    <row r="2453" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2453" s="35" t="s">
+    <row r="2464" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2464" s="35" t="s">
         <v>3304</v>
       </c>
-      <c r="B2453" s="36" t="s">
+      <c r="B2464" s="36" t="s">
         <v>241</v>
       </c>
-      <c r="C2453" s="36" t="s">
+      <c r="C2464" s="36" t="s">
         <v>1967</v>
       </c>
-      <c r="D2453" s="37">
+      <c r="D2464" s="37">
         <v>4301051945</v>
       </c>
-      <c r="E2453" s="36">
+      <c r="E2464" s="36">
         <v>4680115880504</v>
       </c>
-      <c r="F2453" s="38" t="s">
+      <c r="F2464" s="38" t="s">
         <v>259</v>
       </c>
-      <c r="G2453" s="39" t="s">
+      <c r="G2464" s="39" t="s">
         <v>3305</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2453" xr:uid="{569F81D0-594B-46FB-B57B-6536A980B8CA}"/>
+  <autoFilter ref="A1:G2464" xr:uid="{569F81D0-594B-46FB-B57B-6536A980B8CA}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>

--- a/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\ПОКОМ КИ\pokom_ki\WholesaleCustomers\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FAF6B3-B2F8-4254-9497-30C24D456E60}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10B5B25-344E-4E79-B7BF-645D94C572DF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ КИ/pokom_ki/WholesaleCustomers/moduls/1С.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\ПОКОМ КИ\pokom_ki\WholesaleCustomers\moduls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\в бланки заводов\ПОКОМ КИ\pokom_ki\WholesaleCustomers\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF894D9-90D6-4DC9-9AE8-9F7572BDC49B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC450E1-BFCB-4FBA-A8C5-1A63BE71DBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10311" uniqueCount="3342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10471" uniqueCount="3377">
   <si>
     <t>SU002447</t>
   </si>
@@ -10054,6 +10054,111 @@
   </si>
   <si>
     <t>315 Колбаса вареная Молокуша ТМ Вязанка ВЕС, ПОКОМ</t>
+  </si>
+  <si>
+    <t>Колбаса Сервелат Мясорубский ТМ Стародворье с рубленной грудинкой в оболочке фиброуз в вакуум уп, кг</t>
+  </si>
+  <si>
+    <t>Колбаса Сочинка по-европейски с сочной грудинкой ТМ Стародворье оболочке фиброуз в в/у, кг</t>
+  </si>
+  <si>
+    <t>Колбаса Сочинка по-фински с сочным окороком ТМ Стародворье в оболочке фиброуз в в.у., кг</t>
+  </si>
+  <si>
+    <t>Колбаса Сочинка рубленая с сочным окороком ТМ Стародворье в оболочке фиброуз в в.у., кг</t>
+  </si>
+  <si>
+    <t>Ветчина Нежная ТМ Особый рецепт в оболочке полиамид большой батон, кг</t>
+  </si>
+  <si>
+    <t>Колбаса Сливушка ТМ Вязанка в оболочке полиамид вес, кг</t>
+  </si>
+  <si>
+    <t>Ветчина Сливушка с индейкой ТМ Вязанка в оболочке полиамид.Продукт из мяса птицы варенный охлажденны, кг</t>
+  </si>
+  <si>
+    <t>Колбаса Докторская ГОСТ ТМ Стародворские колбасы ТС Вязанка в оболочке вектор УВС2, кг</t>
+  </si>
+  <si>
+    <t>Колбаса вареная Молокуша ТМ Вязанка в оболочке полиамид, кг</t>
+  </si>
+  <si>
+    <t>Сосиски Датские ТМ Зареченские колбасы ТС Зареченские продукты в оболочке полиамид в МГС НТУ, кг</t>
+  </si>
+  <si>
+    <t>Колбаса Филейная (Докторская) ТМ Особый рецепт в оболчке полиамид большой батон, кг</t>
+  </si>
+  <si>
+    <t>Ветчина Дугушка ТМ Стародворье ТС Дугушка в оболочке вектор УВС, кг</t>
+  </si>
+  <si>
+    <t>Колбаса Дугушка ГОСТ ТМ Стародворье ТС Дугушка в полиамидной оболочке, кг</t>
+  </si>
+  <si>
+    <t>Колбаса Дугушка Стародворская ТМ Стародворье ТС Дугушка в полиамидной оболочке, кг</t>
+  </si>
+  <si>
+    <t>Колбаса Салями запеченная ТМ Стародворье ТС Дугушка в оболочке вектор, кг</t>
+  </si>
+  <si>
+    <t>Колбаса Рубленая запеченная ТМ Стародворье ТС Дугушка в оболочке вектор УВС, кг</t>
+  </si>
+  <si>
+    <t>Классическа 0.45 кг Вязанка *Филейская*** (шт.)Колбаса вареная Филейская ТМ Вязанка ТС Классическая в оболочке полиамид 0.45 кг, шт</t>
+  </si>
+  <si>
+    <t>Колбаса Молочная Особая ТМ Особый рецепт в оболочке полиамид, кг</t>
+  </si>
+  <si>
+    <t>Сосиски Вязанка Молочные ТМ Стародворские колбасы ТС Вязанка в оболочке амицел в модиф газ среде УВС, кг</t>
+  </si>
+  <si>
+    <t>Колбаса Нежная ТМ Зареченские ТС Зареченские продукты в оболочке полиамид НТУ, кг</t>
+  </si>
+  <si>
+    <t>Колбаса Со шпиком ТМ Особый рецепт в оболочке полиамид большой батон, кг</t>
+  </si>
+  <si>
+    <t>Сардельки Стародвоские с говядиной ТМ Стародворье в оболочке NDX в модиф.газ.среде, кг</t>
+  </si>
+  <si>
+    <t>P005008</t>
+  </si>
+  <si>
+    <t>Ветчины «Сливушка с индейкой» Весовой п/а ТМ «Вязанка»</t>
+  </si>
+  <si>
+    <t>Основная организация</t>
+  </si>
+  <si>
+    <t>Сардельки Сочные ТМ Особый рецепт в оболочке NDX в модифицированной газовой среде, кг</t>
+  </si>
+  <si>
+    <t>Сосиски Вязанка Сливочные ТМ Стародворские колбасы ТС Вязанка в оболочке амицел в модиф газ среде, кг</t>
+  </si>
+  <si>
+    <t>Сосиски Молочные для завтрака ТМ Особый рецепт в оболочке полиамид в модифицированной газовой среде, кг</t>
+  </si>
+  <si>
+    <t>Сосиски Баварские с сыром ТМ Стародворье в оболочке айпил в МГС 0.35 кг, шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сосиски Баварские ТМ Стародворье в оболочке айпил в МГС 0.35 кг, шт </t>
+  </si>
+  <si>
+    <t>Сосиски Вязанка Сливочные 0.45кг ТМ Стародворские Колбасы ТС Вязанка в оболочке амицел в м.газ.сред., шт</t>
+  </si>
+  <si>
+    <t>Сосиски Вязанка Молочные 0.45кг ТМ Стародворские Колбасы ТС Вязанка в оболочке вискофан в мод.газ.ср, шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">фас.Молочные Для Завтрака ТМ Стародворье 0.400 гр (шт.) </t>
+  </si>
+  <si>
+    <t>Колбаса Швейцарская ТМ Стародворье в оболочке фиброуз в терм.пак.0.17 кг ТУ Стародворские Колбасы, шт</t>
+  </si>
+  <si>
+    <t>Сосиски Сочинки с сочной грудинкой 0.4кг ТМ Стародворье в оболочке полиамид в мод.газ.среде, шт</t>
   </si>
 </sst>
 </file>
@@ -10113,7 +10218,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10159,6 +10264,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -10232,7 +10343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -10357,6 +10468,19 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10643,7 +10767,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G2471"/>
+  <dimension ref="A1:G2503"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="86.140625" style="7" customWidth="1"/>
@@ -63399,6 +63523,742 @@
         <v>3305</v>
       </c>
     </row>
+    <row r="2472" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2472" s="50" t="s">
+        <v>3342</v>
+      </c>
+      <c r="B2472" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2472" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="D2472" s="52">
+        <v>4301031201</v>
+      </c>
+      <c r="E2472" s="51">
+        <v>4680115881563</v>
+      </c>
+      <c r="F2472" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="G2472" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2473" s="50" t="s">
+        <v>3343</v>
+      </c>
+      <c r="B2473" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2473" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2473" s="52">
+        <v>4301031224</v>
+      </c>
+      <c r="E2473" s="51">
+        <v>4680115882683</v>
+      </c>
+      <c r="F2473" s="53" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G2473" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2474" s="50" t="s">
+        <v>3344</v>
+      </c>
+      <c r="B2474" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2474" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2474" s="52">
+        <v>4301031230</v>
+      </c>
+      <c r="E2474" s="51">
+        <v>4680115882690</v>
+      </c>
+      <c r="F2474" s="53" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G2474" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2475" s="50" t="s">
+        <v>3345</v>
+      </c>
+      <c r="B2475" s="51" t="s">
+        <v>661</v>
+      </c>
+      <c r="C2475" s="51" t="s">
+        <v>662</v>
+      </c>
+      <c r="D2475" s="52">
+        <v>4301031221</v>
+      </c>
+      <c r="E2475" s="51">
+        <v>4680115882676</v>
+      </c>
+      <c r="F2475" s="53" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G2475" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2476" s="50" t="s">
+        <v>3346</v>
+      </c>
+      <c r="B2476" s="51" t="s">
+        <v>330</v>
+      </c>
+      <c r="C2476" s="51" t="s">
+        <v>331</v>
+      </c>
+      <c r="D2476" s="52">
+        <v>4301020178</v>
+      </c>
+      <c r="E2476" s="51">
+        <v>4607091383980</v>
+      </c>
+      <c r="F2476" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="G2476" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2477" s="50" t="s">
+        <v>3347</v>
+      </c>
+      <c r="B2477" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2477" s="51" t="s">
+        <v>2741</v>
+      </c>
+      <c r="D2477" s="52">
+        <v>4301011514</v>
+      </c>
+      <c r="E2477" s="51">
+        <v>4680115882133</v>
+      </c>
+      <c r="F2477" s="53" t="s">
+        <v>1480</v>
+      </c>
+      <c r="G2477" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2478" s="50" t="s">
+        <v>3348</v>
+      </c>
+      <c r="B2478" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2478" s="51" t="s">
+        <v>3364</v>
+      </c>
+      <c r="D2478" s="52">
+        <v>4301020391</v>
+      </c>
+      <c r="E2478" s="51">
+        <v>4680115881488</v>
+      </c>
+      <c r="F2478" s="53" t="s">
+        <v>3365</v>
+      </c>
+      <c r="G2478" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2479" s="50" t="s">
+        <v>3349</v>
+      </c>
+      <c r="B2479" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2479" s="51" t="s">
+        <v>2100</v>
+      </c>
+      <c r="D2479" s="52">
+        <v>4301011380</v>
+      </c>
+      <c r="E2479" s="51">
+        <v>4607091385670</v>
+      </c>
+      <c r="F2479" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2479" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2480" s="50" t="s">
+        <v>3350</v>
+      </c>
+      <c r="B2480" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2480" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2480" s="52">
+        <v>4301011468</v>
+      </c>
+      <c r="E2480" s="51">
+        <v>4680115881327</v>
+      </c>
+      <c r="F2480" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2480" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2481" s="50" t="s">
+        <v>3351</v>
+      </c>
+      <c r="B2481" s="51" t="s">
+        <v>992</v>
+      </c>
+      <c r="C2481" s="51" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D2481" s="52">
+        <v>4301052046</v>
+      </c>
+      <c r="E2481" s="51">
+        <v>4640242180533</v>
+      </c>
+      <c r="F2481" s="53" t="s">
+        <v>2744</v>
+      </c>
+      <c r="G2481" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2482" s="50" t="s">
+        <v>3352</v>
+      </c>
+      <c r="B2482" s="51" t="s">
+        <v>2068</v>
+      </c>
+      <c r="C2482" s="51" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D2482" s="52">
+        <v>4301011867</v>
+      </c>
+      <c r="E2482" s="51">
+        <v>4680115884830</v>
+      </c>
+      <c r="F2482" s="53" t="s">
+        <v>2070</v>
+      </c>
+      <c r="G2482" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2483" s="50" t="s">
+        <v>3353</v>
+      </c>
+      <c r="B2483" s="51" t="s">
+        <v>412</v>
+      </c>
+      <c r="C2483" s="51" t="s">
+        <v>2784</v>
+      </c>
+      <c r="D2483" s="52">
+        <v>4301020334</v>
+      </c>
+      <c r="E2483" s="51">
+        <v>4607091388930</v>
+      </c>
+      <c r="F2483" s="53" t="s">
+        <v>413</v>
+      </c>
+      <c r="G2483" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2484" s="50" t="s">
+        <v>3354</v>
+      </c>
+      <c r="B2484" s="51" t="s">
+        <v>401</v>
+      </c>
+      <c r="C2484" s="51" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D2484" s="52">
+        <v>4301011769</v>
+      </c>
+      <c r="E2484" s="51">
+        <v>4607091389067</v>
+      </c>
+      <c r="F2484" s="53" t="s">
+        <v>406</v>
+      </c>
+      <c r="G2484" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2485" s="50" t="s">
+        <v>3355</v>
+      </c>
+      <c r="B2485" s="51" t="s">
+        <v>2120</v>
+      </c>
+      <c r="C2485" s="51" t="s">
+        <v>2121</v>
+      </c>
+      <c r="D2485" s="52">
+        <v>4301011369</v>
+      </c>
+      <c r="E2485" s="51">
+        <v>4680115885226</v>
+      </c>
+      <c r="F2485" s="53" t="s">
+        <v>2122</v>
+      </c>
+      <c r="G2485" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2486" s="50" t="s">
+        <v>3356</v>
+      </c>
+      <c r="B2486" s="51" t="s">
+        <v>417</v>
+      </c>
+      <c r="C2486" s="51" t="s">
+        <v>2634</v>
+      </c>
+      <c r="D2486" s="52">
+        <v>4301031350</v>
+      </c>
+      <c r="E2486" s="51">
+        <v>4680115883093</v>
+      </c>
+      <c r="F2486" s="53" t="s">
+        <v>2635</v>
+      </c>
+      <c r="G2486" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2487" s="50" t="s">
+        <v>3357</v>
+      </c>
+      <c r="B2487" s="51" t="s">
+        <v>416</v>
+      </c>
+      <c r="C2487" s="51" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D2487" s="52">
+        <v>4301031349</v>
+      </c>
+      <c r="E2487" s="51">
+        <v>4680115883116</v>
+      </c>
+      <c r="F2487" s="53" t="s">
+        <v>2571</v>
+      </c>
+      <c r="G2487" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2488" s="50" t="s">
+        <v>3358</v>
+      </c>
+      <c r="B2488" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2488" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2488" s="52">
+        <v>4301011801</v>
+      </c>
+      <c r="E2488" s="51">
+        <v>4680115881419</v>
+      </c>
+      <c r="F2488" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2488" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2489" s="50" t="s">
+        <v>3359</v>
+      </c>
+      <c r="B2489" s="51" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C2489" s="51" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D2489" s="52">
+        <v>4301011869</v>
+      </c>
+      <c r="E2489" s="51">
+        <v>4680115884847</v>
+      </c>
+      <c r="F2489" s="53" t="s">
+        <v>3272</v>
+      </c>
+      <c r="G2489" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2490" s="50" t="s">
+        <v>3360</v>
+      </c>
+      <c r="B2490" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2490" s="51" t="s">
+        <v>2853</v>
+      </c>
+      <c r="D2490" s="52">
+        <v>4301051712</v>
+      </c>
+      <c r="E2490" s="51">
+        <v>4607091386967</v>
+      </c>
+      <c r="F2490" s="53" t="s">
+        <v>2854</v>
+      </c>
+      <c r="G2490" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2491" s="50" t="s">
+        <v>3361</v>
+      </c>
+      <c r="B2491" s="51" t="s">
+        <v>428</v>
+      </c>
+      <c r="C2491" s="51" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D2491" s="52">
+        <v>4301011584</v>
+      </c>
+      <c r="E2491" s="51">
+        <v>4640242180564</v>
+      </c>
+      <c r="F2491" s="53" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G2491" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2492" s="50" t="s">
+        <v>3362</v>
+      </c>
+      <c r="B2492" s="51" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C2492" s="51" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D2492" s="52">
+        <v>4301012083</v>
+      </c>
+      <c r="E2492" s="51">
+        <v>4680115884854</v>
+      </c>
+      <c r="F2492" s="53" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G2492" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2493" s="50" t="s">
+        <v>3363</v>
+      </c>
+      <c r="B2493" s="51" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2493" s="51" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2493" s="52">
+        <v>4301060406</v>
+      </c>
+      <c r="E2493" s="51">
+        <v>4607091384482</v>
+      </c>
+      <c r="F2493" s="53" t="s">
+        <v>2644</v>
+      </c>
+      <c r="G2493" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2494" s="50" t="s">
+        <v>3367</v>
+      </c>
+      <c r="B2494" s="51" t="s">
+        <v>341</v>
+      </c>
+      <c r="C2494" s="51" t="s">
+        <v>3045</v>
+      </c>
+      <c r="D2494" s="52">
+        <v>4301060524</v>
+      </c>
+      <c r="E2494" s="51">
+        <v>4607091384673</v>
+      </c>
+      <c r="F2494" s="53" t="s">
+        <v>2507</v>
+      </c>
+      <c r="G2494" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2495" s="50" t="s">
+        <v>3368</v>
+      </c>
+      <c r="B2495" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2495" s="51" t="s">
+        <v>2851</v>
+      </c>
+      <c r="D2495" s="52">
+        <v>4301051724</v>
+      </c>
+      <c r="E2495" s="51">
+        <v>4607091385168</v>
+      </c>
+      <c r="F2495" s="53" t="s">
+        <v>2852</v>
+      </c>
+      <c r="G2495" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2496" s="50" t="s">
+        <v>3369</v>
+      </c>
+      <c r="B2496" s="51" t="s">
+        <v>353</v>
+      </c>
+      <c r="C2496" s="51" t="s">
+        <v>2508</v>
+      </c>
+      <c r="D2496" s="52">
+        <v>4301051899</v>
+      </c>
+      <c r="E2496" s="51">
+        <v>4607091384246</v>
+      </c>
+      <c r="F2496" s="53" t="s">
+        <v>2509</v>
+      </c>
+      <c r="G2496" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2497" s="50" t="s">
+        <v>3370</v>
+      </c>
+      <c r="B2497" s="51" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C2497" s="51" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D2497" s="52">
+        <v>4301051864</v>
+      </c>
+      <c r="E2497" s="51">
+        <v>4680115883567</v>
+      </c>
+      <c r="F2497" s="53" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G2497" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2498" s="50" t="s">
+        <v>3371</v>
+      </c>
+      <c r="B2498" s="51" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C2498" s="51" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D2498" s="52">
+        <v>4301051461</v>
+      </c>
+      <c r="E2498" s="51">
+        <v>4680115883604</v>
+      </c>
+      <c r="F2498" s="53" t="s">
+        <v>1518</v>
+      </c>
+      <c r="G2498" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2499" s="50" t="s">
+        <v>3372</v>
+      </c>
+      <c r="B2499" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2499" s="51" t="s">
+        <v>2785</v>
+      </c>
+      <c r="D2499" s="52">
+        <v>4301051721</v>
+      </c>
+      <c r="E2499" s="51">
+        <v>4607091385748</v>
+      </c>
+      <c r="F2499" s="53" t="s">
+        <v>2786</v>
+      </c>
+      <c r="G2499" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2500" s="50" t="s">
+        <v>3373</v>
+      </c>
+      <c r="B2500" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2500" s="51" t="s">
+        <v>3056</v>
+      </c>
+      <c r="D2500" s="52">
+        <v>4301051718</v>
+      </c>
+      <c r="E2500" s="51">
+        <v>4607091385731</v>
+      </c>
+      <c r="F2500" s="53" t="s">
+        <v>3057</v>
+      </c>
+      <c r="G2500" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2501" s="50" t="s">
+        <v>3374</v>
+      </c>
+      <c r="B2501" s="51" t="s">
+        <v>354</v>
+      </c>
+      <c r="C2501" s="51" t="s">
+        <v>2787</v>
+      </c>
+      <c r="D2501" s="52">
+        <v>4301051660</v>
+      </c>
+      <c r="E2501" s="51">
+        <v>4607091384253</v>
+      </c>
+      <c r="F2501" s="53" t="s">
+        <v>2788</v>
+      </c>
+      <c r="G2501" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2502" s="50" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B2502" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="C2502" s="51" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D2502" s="52">
+        <v>4301030233</v>
+      </c>
+      <c r="E2502" s="51">
+        <v>4607091388404</v>
+      </c>
+      <c r="F2502" s="53" t="s">
+        <v>279</v>
+      </c>
+      <c r="G2502" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2503" s="50" t="s">
+        <v>3376</v>
+      </c>
+      <c r="B2503" s="51" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2503" s="51" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D2503" s="52">
+        <v>4301051666</v>
+      </c>
+      <c r="E2503" s="51">
+        <v>4680115880092</v>
+      </c>
+      <c r="F2503" s="53" t="s">
+        <v>2060</v>
+      </c>
+      <c r="G2503" s="54" t="s">
+        <v>3366</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G2471" xr:uid="{569F81D0-594B-46FB-B57B-6536A980B8CA}"/>
   <phoneticPr fontId="6" type="noConversion"/>
